--- a/generated/sources/systems/marketing/campaign_calendar_FW26.xlsx
+++ b/generated/sources/systems/marketing/campaign_calendar_FW26.xlsx
@@ -224,7 +224,7 @@
     <author>Mediaplus Milano</author>
     <author>E-com China</author>
     <author>D. Lim</author>
-    <author>Genius team</author>
+    <author>Couture team</author>
     <author>CRM Global</author>
     <author>Camille Lefèvre</author>
     <author>Takuya Suzuki</author>
@@ -268,7 +268,7 @@
     </comment>
     <comment ref="C28" authorId="7" shapeId="0">
       <text>
-        <t>Maire black featured as hero (DC out!)</t>
+        <t>Aurea black featured as hero (DC out!)</t>
       </text>
     </comment>
     <comment ref="C30" authorId="7" shapeId="0">
@@ -619,7 +619,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MONCLER FW26 - MARKETING CALENDAR</t>
+          <t>VALENTINO FW26 - MARKETING CALENDAR</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>POLARIS VIP preview - Shanghai Plaza 66</t>
+          <t>ASTRA VIP preview - Shanghai Plaza 66</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Moncler Genius POLARIS capsule launch</t>
+          <t>Valentino Couture ASTRA capsule launch</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FW26 collection launch (ILVARO, AMBRINE, ARNEB, ROSIERE)</t>
+          <t>FW26 collection launch (IRIDIA, AMALIA, ARTEM, RIVIERA)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Grenoble ski season opening</t>
+          <t>Atelier ski season opening</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CRM newsletter - FW26 icons (Maya, Maire, Hermine)</t>
+          <t>CRM newsletter - FW26 icons (Nova, Aurea, Liviana)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CRM newsletter - Genius Polaris</t>
+          <t>CRM newsletter - Couture Astra</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>POLARIS window takeover Canton Road</t>
+          <t>ASTRA window takeover Canton Road</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ILVARO 'Pink edit' social push</t>
+          <t>IRIDIA 'Pink edit' social push</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Moncler Genius POLARIS capsule launch</t>
+          <t>Valentino Couture ASTRA capsule launch</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Genius team</t>
+          <t>Couture team</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>POLARIS VIP preview - Shanghai Plaza 66</t>
+          <t>ASTRA VIP preview - Shanghai Plaza 66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>POLARIS window takeover Canton Road</t>
+          <t>ASTRA window takeover Canton Road</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FW26 collection launch (ILVARO, AMBRINE, ARNEB, ROSIERE)</t>
+          <t>FW26 collection launch (IRIDIA, AMALIA, ARTEM, RIVIERA)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Grenoble ski season opening</t>
+          <t>Atelier ski season opening</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ILVARO 'Pink edit' social push</t>
+          <t>IRIDIA 'Pink edit' social push</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CRM newsletter - FW26 icons (Maya, Maire, Hermine)</t>
+          <t>CRM newsletter - FW26 icons (Nova, Aurea, Liviana)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Maire black featured as hero (DC out!)</t>
+          <t>Aurea black featured as hero (DC out!)</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CRM newsletter - Genius Polaris</t>
+          <t>CRM newsletter - Couture Astra</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Genius POLARIS launch</t>
+          <t>Couture ASTRA launch</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
